--- a/output/pdf_financials_xlsx/FNI.xlsx
+++ b/output/pdf_financials_xlsx/FNI.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.05484</v>
+        <v>-2.05484</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.003259</v>
+        <v>-1.003259</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.944542</v>
+        <v>-0.944542</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.05484</v>
+        <v>-2.05484</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.003259</v>
+        <v>-1.003259</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.944542</v>
+        <v>-0.944542</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.05484</v>
+        <v>-2.05484</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.003259</v>
+        <v>-1.003259</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.944542</v>
+        <v>-0.944542</v>
       </c>
     </row>
     <row r="24">
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.05484</v>
+        <v>-2.05484</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.003259</v>
+        <v>-1.003259</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.944542</v>
+        <v>-0.944542</v>
       </c>
     </row>
     <row r="28">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.091959</v>
+        <v>-2.017721</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.007355</v>
+        <v>-0.999163</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.949054</v>
+        <v>-0.94003</v>
       </c>
     </row>
     <row r="30">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.244515</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.09571499999999999</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.138522</v>
       </c>
     </row>
     <row r="104">
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.013379</v>
+        <v>-0.257894</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.40195</v>
+        <v>0.497665</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.072104</v>
+        <v>0.066418</v>
       </c>
     </row>
     <row r="107">
@@ -3506,7 +3506,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>-0.244515</v>
       </c>
@@ -4708,13 +4712,13 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2.05484</v>
+        <v>-2.05484</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>1.003259</v>
+        <v>-1.003259</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.944542</v>
+        <v>-0.944542</v>
       </c>
     </row>
     <row r="70">

--- a/output/pdf_financials_xlsx/FNI.xlsx
+++ b/output/pdf_financials_xlsx/FNI.xlsx
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.039905</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02352</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.05484</v>
+        <v>-2.014935</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.003259</v>
+        <v>-0.979739</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.944542</v>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.017721</v>
+        <v>-1.977816</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.999163</v>
+        <v>-0.975643</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.94003</v>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
